--- a/ig/DM-JANVIER-2026/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/DM-JANVIER-2026/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="188">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251028120000</t>
+    <t>20260202120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T12:00:00+01:00</t>
+    <t>2026-02-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>34876-3</t>
+  </si>
+  <si>
+    <t>34895-3</t>
   </si>
   <si>
     <t>39256-3</t>
@@ -837,7 +840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1299,7 +1302,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E35" s="2"/>
     </row>
@@ -1338,20 +1341,20 @@
         <v>33</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -1364,7 +1367,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E40" s="2"/>
     </row>
@@ -1377,7 +1380,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E41" s="2"/>
     </row>
@@ -1416,7 +1419,7 @@
         <v>33</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E44" s="2"/>
     </row>
@@ -1429,7 +1432,7 @@
         <v>33</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="E45" s="2"/>
     </row>
@@ -1442,7 +1445,7 @@
         <v>33</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
     </row>
@@ -1481,7 +1484,7 @@
         <v>33</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E49" s="2"/>
     </row>
@@ -1520,7 +1523,7 @@
         <v>33</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E52" s="2"/>
     </row>
@@ -1533,7 +1536,7 @@
         <v>33</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -1546,7 +1549,7 @@
         <v>33</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="E54" s="2"/>
     </row>
@@ -1559,7 +1562,7 @@
         <v>33</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E55" s="2"/>
     </row>
@@ -1572,7 +1575,7 @@
         <v>33</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E56" s="2"/>
     </row>
@@ -1585,7 +1588,7 @@
         <v>33</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E57" s="2"/>
     </row>
@@ -1598,7 +1601,7 @@
         <v>33</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E58" s="2"/>
     </row>
@@ -1611,7 +1614,7 @@
         <v>33</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -1624,7 +1627,7 @@
         <v>33</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E60" s="2"/>
     </row>
@@ -1637,7 +1640,7 @@
         <v>33</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="E61" s="2"/>
     </row>
@@ -1650,7 +1653,7 @@
         <v>33</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E62" s="2"/>
     </row>
@@ -1663,7 +1666,7 @@
         <v>33</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E63" s="2"/>
     </row>
@@ -1676,7 +1679,7 @@
         <v>33</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E64" s="2"/>
     </row>
@@ -1689,7 +1692,7 @@
         <v>33</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E65" s="2"/>
     </row>
@@ -1702,7 +1705,7 @@
         <v>33</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E66" s="2"/>
     </row>
@@ -1715,20 +1718,20 @@
         <v>33</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="E67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="E68" s="2"/>
     </row>
@@ -1741,7 +1744,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E69" s="2"/>
     </row>
@@ -1806,7 +1809,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E74" s="2"/>
     </row>
@@ -1819,7 +1822,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -1845,7 +1848,7 @@
         <v>33</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E77" s="2"/>
     </row>
@@ -1871,20 +1874,20 @@
         <v>33</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>119</v>
+        <v>34</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -1910,7 +1913,7 @@
         <v>33</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -1936,7 +1939,7 @@
         <v>33</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -1949,7 +1952,7 @@
         <v>33</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E85" s="2"/>
     </row>
@@ -1975,7 +1978,7 @@
         <v>33</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -2001,7 +2004,7 @@
         <v>33</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E89" s="2"/>
     </row>
@@ -2014,7 +2017,7 @@
         <v>33</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -2027,7 +2030,7 @@
         <v>33</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -2040,7 +2043,7 @@
         <v>33</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E92" s="2"/>
     </row>
@@ -2066,7 +2069,7 @@
         <v>33</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E94" s="2"/>
     </row>
@@ -2079,7 +2082,7 @@
         <v>33</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E95" s="2"/>
     </row>
@@ -2105,7 +2108,7 @@
         <v>33</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E97" s="2"/>
     </row>
@@ -2131,7 +2134,7 @@
         <v>33</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E99" s="2"/>
     </row>
@@ -2157,9 +2160,22 @@
         <v>33</v>
       </c>
       <c r="D101" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E101" s="2"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B102" s="2"/>
+      <c r="C102" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D102" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="E101" s="2"/>
+      <c r="E102" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2190,7 +2206,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2207,85 +2223,85 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -2298,7 +2314,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -2311,20 +2327,20 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -2337,33 +2353,33 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2376,20 +2392,20 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -2402,7 +2418,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -2415,7 +2431,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2428,7 +2444,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -2441,7 +2457,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2454,7 +2470,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -2467,7 +2483,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -2480,7 +2496,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -2493,33 +2509,33 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -2532,7 +2548,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -2545,20 +2561,20 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -2571,7 +2587,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2584,20 +2600,20 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2610,7 +2626,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2623,7 +2639,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2636,7 +2652,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -2649,7 +2665,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -2662,7 +2678,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -2675,27 +2691,27 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E40" s="2"/>
     </row>
@@ -2728,7 +2744,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2737,7 +2753,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>30</v>
@@ -2745,14 +2761,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E3" s="2"/>
     </row>
